--- a/doc/Расчет двигателей.xlsx
+++ b/doc/Расчет двигателей.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2022\Project\SE_script\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2019\Project\Work\SE\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C99FF7E-CCF3-45FA-B402-A6CDBBA7E989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807068FA-F10F-4750-AC77-B2327FE9706F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Водородник" sheetId="1" r:id="rId1"/>
-    <sheet name="Атмосферник" sheetId="2" r:id="rId2"/>
+    <sheet name="Ионник" sheetId="3" r:id="rId1"/>
+    <sheet name="Водородник" sheetId="1" r:id="rId2"/>
+    <sheet name="Атмосферник" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="60">
   <si>
     <t>Большой водородник:</t>
   </si>
@@ -188,6 +189,33 @@
   </si>
   <si>
     <t>Большая сетка, Малый водородник:</t>
+  </si>
+  <si>
+    <t>Большой ион:</t>
+  </si>
+  <si>
+    <t>Малый ион:</t>
+  </si>
+  <si>
+    <t>АТМ = 1.0-0.6</t>
+  </si>
+  <si>
+    <t>АТМ = 0.6-0.2</t>
+  </si>
+  <si>
+    <t>АТМ = 0.2-0</t>
+  </si>
+  <si>
+    <t>Малая сетка, Большой ион</t>
+  </si>
+  <si>
+    <t>Малая сетка, Малый  ион</t>
+  </si>
+  <si>
+    <t>Бол сетка, Малый  ион</t>
+  </si>
+  <si>
+    <t>Бол сетка, Большой  ион</t>
   </si>
 </sst>
 </file>
@@ -661,6 +689,659 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4F53A4-9A07-445E-9B8A-9BE593D40D5F}">
+  <dimension ref="A1:O49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="13"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3">
+        <v>4320</v>
+      </c>
+      <c r="C3">
+        <v>440</v>
+      </c>
+      <c r="E3">
+        <v>33.6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4">
+        <v>345</v>
+      </c>
+      <c r="C4">
+        <v>35</v>
+      </c>
+      <c r="E4">
+        <v>2.4</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L7" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8">
+        <v>172</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>3.36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>0.2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9">
+        <v>0.05</v>
+      </c>
+      <c r="I9">
+        <v>0.2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="12">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="14">
+        <v>5000</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="11">
+        <f>B17*10</f>
+        <v>50000</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="14">
+        <v>1</v>
+      </c>
+      <c r="C20" s="11">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="11">
+        <f>B18*C20</f>
+        <v>60000</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="11">
+        <f>B3*B24</f>
+        <v>4320</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="11">
+        <f>B4*B24</f>
+        <v>345</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="11">
+        <f>B8*B24</f>
+        <v>172</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="11">
+        <f>B9*B24</f>
+        <v>14</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="17"/>
+      <c r="C35" s="18"/>
+      <c r="E35" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="20"/>
+      <c r="G35" s="21"/>
+      <c r="I35" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="J35" s="20"/>
+      <c r="K35" s="21"/>
+      <c r="M35" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N35" s="20"/>
+      <c r="O35" s="21"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="5">
+        <f>B21/B30</f>
+        <v>348.83720930232556</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="5">
+        <f>B21/B31</f>
+        <v>4285.7142857142853</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" s="5">
+        <f>B21/B28</f>
+        <v>173.91304347826087</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="N36" s="5">
+        <f>B21/B27</f>
+        <v>13.888888888888889</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="5">
+        <f>B36*1.5</f>
+        <v>523.25581395348831</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="5">
+        <f>F36*1.5</f>
+        <v>6428.5714285714275</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J38" s="5">
+        <f>J36*1.5</f>
+        <v>260.86956521739131</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N38" s="5">
+        <f>N36*1.5</f>
+        <v>20.833333333333336</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="9">
+        <f>ROUNDUP(B38,0)</f>
+        <v>524</v>
+      </c>
+      <c r="C39" s="5"/>
+      <c r="E39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="9">
+        <f>ROUNDUP(F38,0)</f>
+        <v>6429</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="I39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J39" s="9">
+        <f>ROUNDUP(J38,0)</f>
+        <v>261</v>
+      </c>
+      <c r="K39" s="5"/>
+      <c r="M39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N39" s="9">
+        <f>ROUNDUP(N38,0)</f>
+        <v>21</v>
+      </c>
+      <c r="O39" s="5"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5">
+        <f>B39*E8</f>
+        <v>1760.6399999999999</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F41" s="5">
+        <f>F39*E9</f>
+        <v>1285.8000000000002</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J41" s="5">
+        <f>J39*E4</f>
+        <v>626.4</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N41" s="5">
+        <f>N39*E3</f>
+        <v>705.6</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="5">
+        <f>B41/I8</f>
+        <v>440.15999999999997</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="E43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43" s="5">
+        <f>F41/I8</f>
+        <v>321.45000000000005</v>
+      </c>
+      <c r="G43" s="5"/>
+      <c r="I43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J43" s="5">
+        <f>J41/I3</f>
+        <v>52.199999999999996</v>
+      </c>
+      <c r="K43" s="5"/>
+      <c r="M43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N43" s="5">
+        <f>N41/I3</f>
+        <v>58.800000000000004</v>
+      </c>
+      <c r="O43" s="5"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="9">
+        <f>ROUNDUP(B43,0)</f>
+        <v>441</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="E44" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F44" s="9">
+        <f>ROUNDUP(F43,0)</f>
+        <v>322</v>
+      </c>
+      <c r="G44" s="5"/>
+      <c r="I44" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J44" s="9">
+        <f>ROUNDUP(J43,0)</f>
+        <v>53</v>
+      </c>
+      <c r="K44" s="5"/>
+      <c r="M44" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="N44" s="9">
+        <f>ROUNDUP(N43,0)</f>
+        <v>59</v>
+      </c>
+      <c r="O44" s="5"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C46">
+        <f>F39/B39</f>
+        <v>12.269083969465649</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L48">
+        <f>J39/N39</f>
+        <v>12.428571428571429</v>
+      </c>
+    </row>
+    <row r="49" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G49">
+        <f>9*3</f>
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="M35:O35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1167,7 +1848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/doc/Расчет двигателей.xlsx
+++ b/doc/Расчет двигателей.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2019\Project\Work\SE\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807068FA-F10F-4750-AC77-B2327FE9706F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448D3A15-4B1A-428C-81C7-8CE6949B2439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ионник" sheetId="3" r:id="rId1"/>
@@ -388,9 +388,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -408,6 +405,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1004,26 +1004,26 @@
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="18"/>
-      <c r="E35" s="19" t="s">
+      <c r="B35" s="16"/>
+      <c r="C35" s="17"/>
+      <c r="E35" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="F35" s="20"/>
-      <c r="G35" s="21"/>
-      <c r="I35" s="19" t="s">
+      <c r="F35" s="19"/>
+      <c r="G35" s="20"/>
+      <c r="I35" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="J35" s="20"/>
-      <c r="K35" s="21"/>
-      <c r="M35" s="19" t="s">
+      <c r="J35" s="19"/>
+      <c r="K35" s="20"/>
+      <c r="M35" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="N35" s="20"/>
-      <c r="O35" s="21"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="20"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
@@ -1505,11 +1505,11 @@
         <v>7</v>
       </c>
       <c r="B22" s="6">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="C22" s="7">
         <f>B22*10</f>
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="D22" s="6">
         <v>30</v>
@@ -1518,30 +1518,30 @@
     </row>
     <row r="24" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="G24" s="15" t="s">
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="G24" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="L24" s="15" t="s">
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="L24" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
-      <c r="Q24" s="15" t="s">
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="Q24" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="R24" s="15"/>
-      <c r="S24" s="15"/>
-      <c r="T24" s="15"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="21"/>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B25" s="5">
         <f>C22/$B$8</f>
-        <v>31.25</v>
+        <v>62.5</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>16</v>
@@ -1558,7 +1558,7 @@
       <c r="E25" s="5"/>
       <c r="G25" s="5">
         <f>$C$22/B9</f>
-        <v>153.0612244897959</v>
+        <v>306.12244897959181</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>16</v>
@@ -1567,7 +1567,7 @@
       <c r="J25" s="5"/>
       <c r="L25" s="5">
         <f>C22/B3</f>
-        <v>2.0833333333333335</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>16</v>
@@ -1576,7 +1576,7 @@
       <c r="O25" s="5"/>
       <c r="Q25" s="5">
         <f>$C$22/B4</f>
-        <v>13.636363636363637</v>
+        <v>27.272727272727273</v>
       </c>
       <c r="R25" s="5" t="s">
         <v>16</v>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B26" s="5">
         <f>ROUNDUP(B25,0)</f>
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>16</v>
@@ -1599,7 +1599,7 @@
       <c r="E26" s="5"/>
       <c r="G26" s="5">
         <f>ROUNDUP(G25,0)</f>
-        <v>154</v>
+        <v>307</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>16</v>
@@ -1608,7 +1608,7 @@
       <c r="J26" s="5"/>
       <c r="L26" s="5">
         <f>ROUNDUP(L25,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M26" s="5" t="s">
         <v>16</v>
@@ -1617,7 +1617,7 @@
       <c r="O26" s="5"/>
       <c r="Q26" s="5">
         <f>ROUNDUP(Q25,0)</f>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="R26" s="5" t="s">
         <v>16</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B27" s="10">
         <f>B26*150%</f>
-        <v>48</v>
+        <v>94.5</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>16</v>
@@ -1640,7 +1640,7 @@
       <c r="E27" s="5"/>
       <c r="G27" s="10">
         <f>G26*150%</f>
-        <v>231</v>
+        <v>460.5</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>16</v>
@@ -1649,26 +1649,26 @@
       <c r="J27" s="5"/>
       <c r="L27" s="5">
         <f>L26*150%</f>
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="N27" s="10">
         <f>ROUNDUP(L27,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O27" s="5"/>
       <c r="Q27" s="5">
         <f>Q26*150%</f>
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="R27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="S27" s="10">
         <f>ROUNDUP(Q27,0)</f>
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="T27" s="5"/>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B28" s="5">
         <f>B27*E8</f>
-        <v>28800</v>
+        <v>56700</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>11</v>
@@ -1687,7 +1687,7 @@
       <c r="E28" s="5"/>
       <c r="G28" s="5">
         <f>G27*E9</f>
-        <v>23100</v>
+        <v>46050</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>11</v>
@@ -1696,7 +1696,7 @@
       <c r="J28" s="5"/>
       <c r="L28" s="5">
         <f>N27*E3</f>
-        <v>37500</v>
+        <v>60000</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>11</v>
@@ -1705,7 +1705,7 @@
       <c r="O28" s="5"/>
       <c r="Q28" s="5">
         <f>S27*E4</f>
-        <v>25200</v>
+        <v>50400</v>
       </c>
       <c r="R28" s="5" t="s">
         <v>11</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B29" s="5">
         <f>B28*60*D22</f>
-        <v>51840000</v>
+        <v>102060000</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>11</v>
@@ -1728,7 +1728,7 @@
       <c r="E29" s="5"/>
       <c r="G29" s="5">
         <f>G28*60*$D$22</f>
-        <v>41580000</v>
+        <v>82890000</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>11</v>
@@ -1737,7 +1737,7 @@
       <c r="J29" s="5"/>
       <c r="L29" s="5">
         <f>L28*60*D22</f>
-        <v>67500000</v>
+        <v>108000000</v>
       </c>
       <c r="M29" s="5" t="s">
         <v>11</v>
@@ -1746,7 +1746,7 @@
       <c r="O29" s="5"/>
       <c r="Q29" s="5">
         <f>Q28*60*$D$22</f>
-        <v>45360000</v>
+        <v>90720000</v>
       </c>
       <c r="R29" s="5" t="s">
         <v>11</v>
@@ -1760,28 +1760,28 @@
       </c>
       <c r="B30" s="10">
         <f>B29/H8</f>
-        <v>103.68</v>
+        <v>204.12</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="G30" s="10">
         <f>G29/H8</f>
-        <v>83.16</v>
+        <v>165.78</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="L30" s="10">
         <f>L29/H3</f>
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
       <c r="Q30" s="10">
         <f>Q29/H3</f>
-        <v>3.024</v>
+        <v>6.048</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -1793,28 +1793,28 @@
       </c>
       <c r="B31" s="10">
         <f>B29/H9</f>
-        <v>3456</v>
+        <v>6804</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="G31" s="10">
         <f>G29/H9</f>
-        <v>2772</v>
+        <v>5526</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="L31" s="10">
         <f>L29/H4</f>
-        <v>67.5</v>
+        <v>108</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
       <c r="Q31" s="10">
         <f>Q29/H4</f>
-        <v>45.36</v>
+        <v>90.72</v>
       </c>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
@@ -1823,17 +1823,17 @@
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33">
         <f>G26/B26</f>
-        <v>4.8125</v>
+        <v>4.8730158730158726</v>
       </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="O34">
         <f>S27/N27</f>
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="P34">
         <f>S27/N27</f>
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
     </row>
   </sheetData>
@@ -2145,26 +2145,26 @@
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="18"/>
-      <c r="E35" s="19" t="s">
+      <c r="B35" s="16"/>
+      <c r="C35" s="17"/>
+      <c r="E35" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F35" s="20"/>
-      <c r="G35" s="21"/>
-      <c r="I35" s="19" t="s">
+      <c r="F35" s="19"/>
+      <c r="G35" s="20"/>
+      <c r="I35" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="J35" s="20"/>
-      <c r="K35" s="21"/>
-      <c r="M35" s="19" t="s">
+      <c r="J35" s="19"/>
+      <c r="K35" s="20"/>
+      <c r="M35" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="N35" s="20"/>
-      <c r="O35" s="21"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="20"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">

--- a/doc/Расчет двигателей.xlsx
+++ b/doc/Расчет двигателей.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2019\Project\Work\SE\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448D3A15-4B1A-428C-81C7-8CE6949B2439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65FF668-FB66-4989-AB89-8953E76FB943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/doc/Расчет двигателей.xlsx
+++ b/doc/Расчет двигателей.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2019\Project\Work\SE\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65FF668-FB66-4989-AB89-8953E76FB943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99664ADB-7B34-4EBC-B68D-CA74081E12A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1505,11 +1505,11 @@
         <v>7</v>
       </c>
       <c r="B22" s="6">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="C22" s="7">
         <f>B22*10</f>
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="D22" s="6">
         <v>30</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B25" s="5">
         <f>C22/$B$8</f>
-        <v>62.5</v>
+        <v>31.25</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>16</v>
@@ -1558,7 +1558,7 @@
       <c r="E25" s="5"/>
       <c r="G25" s="5">
         <f>$C$22/B9</f>
-        <v>306.12244897959181</v>
+        <v>153.0612244897959</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>16</v>
@@ -1567,7 +1567,7 @@
       <c r="J25" s="5"/>
       <c r="L25" s="5">
         <f>C22/B3</f>
-        <v>4.166666666666667</v>
+        <v>2.0833333333333335</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>16</v>
@@ -1576,7 +1576,7 @@
       <c r="O25" s="5"/>
       <c r="Q25" s="5">
         <f>$C$22/B4</f>
-        <v>27.272727272727273</v>
+        <v>13.636363636363637</v>
       </c>
       <c r="R25" s="5" t="s">
         <v>16</v>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B26" s="5">
         <f>ROUNDUP(B25,0)</f>
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>16</v>
@@ -1599,7 +1599,7 @@
       <c r="E26" s="5"/>
       <c r="G26" s="5">
         <f>ROUNDUP(G25,0)</f>
-        <v>307</v>
+        <v>154</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>16</v>
@@ -1608,7 +1608,7 @@
       <c r="J26" s="5"/>
       <c r="L26" s="5">
         <f>ROUNDUP(L25,0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M26" s="5" t="s">
         <v>16</v>
@@ -1617,7 +1617,7 @@
       <c r="O26" s="5"/>
       <c r="Q26" s="5">
         <f>ROUNDUP(Q25,0)</f>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="R26" s="5" t="s">
         <v>16</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B27" s="10">
         <f>B26*150%</f>
-        <v>94.5</v>
+        <v>48</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>16</v>
@@ -1640,7 +1640,7 @@
       <c r="E27" s="5"/>
       <c r="G27" s="10">
         <f>G26*150%</f>
-        <v>460.5</v>
+        <v>231</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>16</v>
@@ -1649,26 +1649,26 @@
       <c r="J27" s="5"/>
       <c r="L27" s="5">
         <f>L26*150%</f>
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="N27" s="10">
         <f>ROUNDUP(L27,0)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O27" s="5"/>
       <c r="Q27" s="5">
         <f>Q26*150%</f>
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="R27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="S27" s="10">
         <f>ROUNDUP(Q27,0)</f>
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="T27" s="5"/>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B28" s="5">
         <f>B27*E8</f>
-        <v>56700</v>
+        <v>28800</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>11</v>
@@ -1687,7 +1687,7 @@
       <c r="E28" s="5"/>
       <c r="G28" s="5">
         <f>G27*E9</f>
-        <v>46050</v>
+        <v>23100</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>11</v>
@@ -1696,7 +1696,7 @@
       <c r="J28" s="5"/>
       <c r="L28" s="5">
         <f>N27*E3</f>
-        <v>60000</v>
+        <v>37500</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>11</v>
@@ -1705,7 +1705,7 @@
       <c r="O28" s="5"/>
       <c r="Q28" s="5">
         <f>S27*E4</f>
-        <v>50400</v>
+        <v>25200</v>
       </c>
       <c r="R28" s="5" t="s">
         <v>11</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B29" s="5">
         <f>B28*60*D22</f>
-        <v>102060000</v>
+        <v>51840000</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>11</v>
@@ -1728,7 +1728,7 @@
       <c r="E29" s="5"/>
       <c r="G29" s="5">
         <f>G28*60*$D$22</f>
-        <v>82890000</v>
+        <v>41580000</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>11</v>
@@ -1737,7 +1737,7 @@
       <c r="J29" s="5"/>
       <c r="L29" s="5">
         <f>L28*60*D22</f>
-        <v>108000000</v>
+        <v>67500000</v>
       </c>
       <c r="M29" s="5" t="s">
         <v>11</v>
@@ -1746,7 +1746,7 @@
       <c r="O29" s="5"/>
       <c r="Q29" s="5">
         <f>Q28*60*$D$22</f>
-        <v>90720000</v>
+        <v>45360000</v>
       </c>
       <c r="R29" s="5" t="s">
         <v>11</v>
@@ -1760,28 +1760,28 @@
       </c>
       <c r="B30" s="10">
         <f>B29/H8</f>
-        <v>204.12</v>
+        <v>103.68</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="G30" s="10">
         <f>G29/H8</f>
-        <v>165.78</v>
+        <v>83.16</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="L30" s="10">
         <f>L29/H3</f>
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
       <c r="Q30" s="10">
         <f>Q29/H3</f>
-        <v>6.048</v>
+        <v>3.024</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -1793,28 +1793,28 @@
       </c>
       <c r="B31" s="10">
         <f>B29/H9</f>
-        <v>6804</v>
+        <v>3456</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="G31" s="10">
         <f>G29/H9</f>
-        <v>5526</v>
+        <v>2772</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="L31" s="10">
         <f>L29/H4</f>
-        <v>108</v>
+        <v>67.5</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
       <c r="Q31" s="10">
         <f>Q29/H4</f>
-        <v>90.72</v>
+        <v>45.36</v>
       </c>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
@@ -1823,17 +1823,17 @@
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33">
         <f>G26/B26</f>
-        <v>4.8730158730158726</v>
+        <v>4.8125</v>
       </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="O34">
         <f>S27/N27</f>
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="P34">
         <f>S27/N27</f>
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/doc/Расчет двигателей.xlsx
+++ b/doc/Расчет двигателей.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2019\Project\Work\SE\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2022\Project\SE_script\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99664ADB-7B34-4EBC-B68D-CA74081E12A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8ACAC4-0163-4B28-93F1-6BD70A378D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1505,11 +1505,11 @@
         <v>7</v>
       </c>
       <c r="B22" s="6">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="C22" s="7">
         <f>B22*10</f>
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="D22" s="6">
         <v>30</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B25" s="5">
         <f>C22/$B$8</f>
-        <v>31.25</v>
+        <v>10.416666666666666</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>16</v>
@@ -1558,7 +1558,7 @@
       <c r="E25" s="5"/>
       <c r="G25" s="5">
         <f>$C$22/B9</f>
-        <v>153.0612244897959</v>
+        <v>51.020408163265309</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>16</v>
@@ -1567,7 +1567,7 @@
       <c r="J25" s="5"/>
       <c r="L25" s="5">
         <f>C22/B3</f>
-        <v>2.0833333333333335</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>16</v>
@@ -1576,7 +1576,7 @@
       <c r="O25" s="5"/>
       <c r="Q25" s="5">
         <f>$C$22/B4</f>
-        <v>13.636363636363637</v>
+        <v>4.5454545454545459</v>
       </c>
       <c r="R25" s="5" t="s">
         <v>16</v>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B26" s="5">
         <f>ROUNDUP(B25,0)</f>
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>16</v>
@@ -1599,7 +1599,7 @@
       <c r="E26" s="5"/>
       <c r="G26" s="5">
         <f>ROUNDUP(G25,0)</f>
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>16</v>
@@ -1608,7 +1608,7 @@
       <c r="J26" s="5"/>
       <c r="L26" s="5">
         <f>ROUNDUP(L25,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M26" s="5" t="s">
         <v>16</v>
@@ -1617,7 +1617,7 @@
       <c r="O26" s="5"/>
       <c r="Q26" s="5">
         <f>ROUNDUP(Q25,0)</f>
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="R26" s="5" t="s">
         <v>16</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B27" s="10">
         <f>B26*150%</f>
-        <v>48</v>
+        <v>16.5</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>16</v>
@@ -1640,7 +1640,7 @@
       <c r="E27" s="5"/>
       <c r="G27" s="10">
         <f>G26*150%</f>
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>16</v>
@@ -1649,26 +1649,26 @@
       <c r="J27" s="5"/>
       <c r="L27" s="5">
         <f>L26*150%</f>
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="N27" s="10">
         <f>ROUNDUP(L27,0)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O27" s="5"/>
       <c r="Q27" s="5">
         <f>Q26*150%</f>
-        <v>21</v>
+        <v>7.5</v>
       </c>
       <c r="R27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="S27" s="10">
         <f>ROUNDUP(Q27,0)</f>
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="T27" s="5"/>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B28" s="5">
         <f>B27*E8</f>
-        <v>28800</v>
+        <v>9900</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>11</v>
@@ -1687,7 +1687,7 @@
       <c r="E28" s="5"/>
       <c r="G28" s="5">
         <f>G27*E9</f>
-        <v>23100</v>
+        <v>7800</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>11</v>
@@ -1696,7 +1696,7 @@
       <c r="J28" s="5"/>
       <c r="L28" s="5">
         <f>N27*E3</f>
-        <v>37500</v>
+        <v>15000</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>11</v>
@@ -1705,7 +1705,7 @@
       <c r="O28" s="5"/>
       <c r="Q28" s="5">
         <f>S27*E4</f>
-        <v>25200</v>
+        <v>9600</v>
       </c>
       <c r="R28" s="5" t="s">
         <v>11</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B29" s="5">
         <f>B28*60*D22</f>
-        <v>51840000</v>
+        <v>17820000</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>11</v>
@@ -1728,7 +1728,7 @@
       <c r="E29" s="5"/>
       <c r="G29" s="5">
         <f>G28*60*$D$22</f>
-        <v>41580000</v>
+        <v>14040000</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>11</v>
@@ -1737,7 +1737,7 @@
       <c r="J29" s="5"/>
       <c r="L29" s="5">
         <f>L28*60*D22</f>
-        <v>67500000</v>
+        <v>27000000</v>
       </c>
       <c r="M29" s="5" t="s">
         <v>11</v>
@@ -1746,7 +1746,7 @@
       <c r="O29" s="5"/>
       <c r="Q29" s="5">
         <f>Q28*60*$D$22</f>
-        <v>45360000</v>
+        <v>17280000</v>
       </c>
       <c r="R29" s="5" t="s">
         <v>11</v>
@@ -1760,28 +1760,28 @@
       </c>
       <c r="B30" s="10">
         <f>B29/H8</f>
-        <v>103.68</v>
+        <v>35.64</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="G30" s="10">
         <f>G29/H8</f>
-        <v>83.16</v>
+        <v>28.08</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="L30" s="10">
         <f>L29/H3</f>
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
       <c r="Q30" s="10">
         <f>Q29/H3</f>
-        <v>3.024</v>
+        <v>1.1519999999999999</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -1793,28 +1793,28 @@
       </c>
       <c r="B31" s="10">
         <f>B29/H9</f>
-        <v>3456</v>
+        <v>1188</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="G31" s="10">
         <f>G29/H9</f>
-        <v>2772</v>
+        <v>936</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="L31" s="10">
         <f>L29/H4</f>
-        <v>67.5</v>
+        <v>27</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
       <c r="Q31" s="10">
         <f>Q29/H4</f>
-        <v>45.36</v>
+        <v>17.28</v>
       </c>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
@@ -1823,17 +1823,17 @@
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33">
         <f>G26/B26</f>
-        <v>4.8125</v>
+        <v>4.7272727272727275</v>
       </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="O34">
         <f>S27/N27</f>
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P34">
         <f>S27/N27</f>
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/doc/Расчет двигателей.xlsx
+++ b/doc/Расчет двигателей.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2022\Project\SE_script\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8ACAC4-0163-4B28-93F1-6BD70A378D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2477B67D-A0B7-44D5-92C7-B031943E6085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2070" yWindow="300" windowWidth="17250" windowHeight="14865" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ионник" sheetId="3" r:id="rId1"/>
@@ -1347,7 +1347,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -1505,11 +1505,11 @@
         <v>7</v>
       </c>
       <c r="B22" s="6">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="C22" s="7">
         <f>B22*10</f>
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="D22" s="6">
         <v>30</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B25" s="5">
         <f>C22/$B$8</f>
-        <v>10.416666666666666</v>
+        <v>62.5</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>16</v>
@@ -1558,7 +1558,7 @@
       <c r="E25" s="5"/>
       <c r="G25" s="5">
         <f>$C$22/B9</f>
-        <v>51.020408163265309</v>
+        <v>306.12244897959181</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>16</v>
@@ -1567,7 +1567,7 @@
       <c r="J25" s="5"/>
       <c r="L25" s="5">
         <f>C22/B3</f>
-        <v>0.69444444444444442</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>16</v>
@@ -1576,7 +1576,7 @@
       <c r="O25" s="5"/>
       <c r="Q25" s="5">
         <f>$C$22/B4</f>
-        <v>4.5454545454545459</v>
+        <v>27.272727272727273</v>
       </c>
       <c r="R25" s="5" t="s">
         <v>16</v>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B26" s="5">
         <f>ROUNDUP(B25,0)</f>
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>16</v>
@@ -1599,7 +1599,7 @@
       <c r="E26" s="5"/>
       <c r="G26" s="5">
         <f>ROUNDUP(G25,0)</f>
-        <v>52</v>
+        <v>307</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>16</v>
@@ -1608,7 +1608,7 @@
       <c r="J26" s="5"/>
       <c r="L26" s="5">
         <f>ROUNDUP(L25,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M26" s="5" t="s">
         <v>16</v>
@@ -1617,7 +1617,7 @@
       <c r="O26" s="5"/>
       <c r="Q26" s="5">
         <f>ROUNDUP(Q25,0)</f>
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="R26" s="5" t="s">
         <v>16</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B27" s="10">
         <f>B26*150%</f>
-        <v>16.5</v>
+        <v>94.5</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>16</v>
@@ -1640,7 +1640,7 @@
       <c r="E27" s="5"/>
       <c r="G27" s="10">
         <f>G26*150%</f>
-        <v>78</v>
+        <v>460.5</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>16</v>
@@ -1649,26 +1649,26 @@
       <c r="J27" s="5"/>
       <c r="L27" s="5">
         <f>L26*150%</f>
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="N27" s="10">
         <f>ROUNDUP(L27,0)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O27" s="5"/>
       <c r="Q27" s="5">
         <f>Q26*150%</f>
-        <v>7.5</v>
+        <v>42</v>
       </c>
       <c r="R27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="S27" s="10">
         <f>ROUNDUP(Q27,0)</f>
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="T27" s="5"/>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B28" s="5">
         <f>B27*E8</f>
-        <v>9900</v>
+        <v>56700</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>11</v>
@@ -1687,7 +1687,7 @@
       <c r="E28" s="5"/>
       <c r="G28" s="5">
         <f>G27*E9</f>
-        <v>7800</v>
+        <v>46050</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>11</v>
@@ -1696,7 +1696,7 @@
       <c r="J28" s="5"/>
       <c r="L28" s="5">
         <f>N27*E3</f>
-        <v>15000</v>
+        <v>60000</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>11</v>
@@ -1705,7 +1705,7 @@
       <c r="O28" s="5"/>
       <c r="Q28" s="5">
         <f>S27*E4</f>
-        <v>9600</v>
+        <v>50400</v>
       </c>
       <c r="R28" s="5" t="s">
         <v>11</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B29" s="5">
         <f>B28*60*D22</f>
-        <v>17820000</v>
+        <v>102060000</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>11</v>
@@ -1728,7 +1728,7 @@
       <c r="E29" s="5"/>
       <c r="G29" s="5">
         <f>G28*60*$D$22</f>
-        <v>14040000</v>
+        <v>82890000</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>11</v>
@@ -1737,7 +1737,7 @@
       <c r="J29" s="5"/>
       <c r="L29" s="5">
         <f>L28*60*D22</f>
-        <v>27000000</v>
+        <v>108000000</v>
       </c>
       <c r="M29" s="5" t="s">
         <v>11</v>
@@ -1746,7 +1746,7 @@
       <c r="O29" s="5"/>
       <c r="Q29" s="5">
         <f>Q28*60*$D$22</f>
-        <v>17280000</v>
+        <v>90720000</v>
       </c>
       <c r="R29" s="5" t="s">
         <v>11</v>
@@ -1760,28 +1760,28 @@
       </c>
       <c r="B30" s="10">
         <f>B29/H8</f>
-        <v>35.64</v>
+        <v>204.12</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="G30" s="10">
         <f>G29/H8</f>
-        <v>28.08</v>
+        <v>165.78</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="L30" s="10">
         <f>L29/H3</f>
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
       <c r="Q30" s="10">
         <f>Q29/H3</f>
-        <v>1.1519999999999999</v>
+        <v>6.048</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -1793,28 +1793,28 @@
       </c>
       <c r="B31" s="10">
         <f>B29/H9</f>
-        <v>1188</v>
+        <v>6804</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="G31" s="10">
         <f>G29/H9</f>
-        <v>936</v>
+        <v>5526</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="L31" s="10">
         <f>L29/H4</f>
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
       <c r="Q31" s="10">
         <f>Q29/H4</f>
-        <v>17.28</v>
+        <v>90.72</v>
       </c>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
@@ -1823,17 +1823,17 @@
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33">
         <f>G26/B26</f>
-        <v>4.7272727272727275</v>
+        <v>4.8730158730158726</v>
       </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="O34">
         <f>S27/N27</f>
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P34">
         <f>S27/N27</f>
-        <v>4</v>
+        <v>5.25</v>
       </c>
     </row>
   </sheetData>

--- a/doc/Расчет двигателей.xlsx
+++ b/doc/Расчет двигателей.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2022\Project\SE_script\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2477B67D-A0B7-44D5-92C7-B031943E6085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2070" yWindow="300" windowWidth="17250" windowHeight="14865" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2070" yWindow="300" windowWidth="17250" windowHeight="14865" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Ионник" sheetId="3" r:id="rId1"/>
     <sheet name="Водородник" sheetId="1" r:id="rId2"/>
     <sheet name="Атмосферник" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -221,7 +220,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -689,7 +688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4F53A4-9A07-445E-9B8A-9BE593D40D5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1342,7 +1341,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1505,11 +1504,11 @@
         <v>7</v>
       </c>
       <c r="B22" s="6">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="C22" s="7">
         <f>B22*10</f>
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="D22" s="6">
         <v>30</v>
@@ -1549,7 +1548,7 @@
       </c>
       <c r="B25" s="5">
         <f>C22/$B$8</f>
-        <v>62.5</v>
+        <v>68.75</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>16</v>
@@ -1558,7 +1557,7 @@
       <c r="E25" s="5"/>
       <c r="G25" s="5">
         <f>$C$22/B9</f>
-        <v>306.12244897959181</v>
+        <v>336.73469387755102</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>16</v>
@@ -1567,7 +1566,7 @@
       <c r="J25" s="5"/>
       <c r="L25" s="5">
         <f>C22/B3</f>
-        <v>4.166666666666667</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>16</v>
@@ -1576,7 +1575,7 @@
       <c r="O25" s="5"/>
       <c r="Q25" s="5">
         <f>$C$22/B4</f>
-        <v>27.272727272727273</v>
+        <v>30</v>
       </c>
       <c r="R25" s="5" t="s">
         <v>16</v>
@@ -1590,7 +1589,7 @@
       </c>
       <c r="B26" s="5">
         <f>ROUNDUP(B25,0)</f>
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>16</v>
@@ -1599,7 +1598,7 @@
       <c r="E26" s="5"/>
       <c r="G26" s="5">
         <f>ROUNDUP(G25,0)</f>
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>16</v>
@@ -1617,7 +1616,7 @@
       <c r="O26" s="5"/>
       <c r="Q26" s="5">
         <f>ROUNDUP(Q25,0)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R26" s="5" t="s">
         <v>16</v>
@@ -1631,7 +1630,7 @@
       </c>
       <c r="B27" s="10">
         <f>B26*150%</f>
-        <v>94.5</v>
+        <v>103.5</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>16</v>
@@ -1640,7 +1639,7 @@
       <c r="E27" s="5"/>
       <c r="G27" s="10">
         <f>G26*150%</f>
-        <v>460.5</v>
+        <v>505.5</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>16</v>
@@ -1661,14 +1660,14 @@
       <c r="O27" s="5"/>
       <c r="Q27" s="5">
         <f>Q26*150%</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="S27" s="10">
         <f>ROUNDUP(Q27,0)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T27" s="5"/>
     </row>
@@ -1678,7 +1677,7 @@
       </c>
       <c r="B28" s="5">
         <f>B27*E8</f>
-        <v>56700</v>
+        <v>62100</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>11</v>
@@ -1687,7 +1686,7 @@
       <c r="E28" s="5"/>
       <c r="G28" s="5">
         <f>G27*E9</f>
-        <v>46050</v>
+        <v>50550</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>11</v>
@@ -1705,7 +1704,7 @@
       <c r="O28" s="5"/>
       <c r="Q28" s="5">
         <f>S27*E4</f>
-        <v>50400</v>
+        <v>54000</v>
       </c>
       <c r="R28" s="5" t="s">
         <v>11</v>
@@ -1719,7 +1718,7 @@
       </c>
       <c r="B29" s="5">
         <f>B28*60*D22</f>
-        <v>102060000</v>
+        <v>111780000</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>11</v>
@@ -1728,7 +1727,7 @@
       <c r="E29" s="5"/>
       <c r="G29" s="5">
         <f>G28*60*$D$22</f>
-        <v>82890000</v>
+        <v>90990000</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>11</v>
@@ -1746,7 +1745,7 @@
       <c r="O29" s="5"/>
       <c r="Q29" s="5">
         <f>Q28*60*$D$22</f>
-        <v>90720000</v>
+        <v>97200000</v>
       </c>
       <c r="R29" s="5" t="s">
         <v>11</v>
@@ -1760,14 +1759,14 @@
       </c>
       <c r="B30" s="10">
         <f>B29/H8</f>
-        <v>204.12</v>
+        <v>223.56</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="G30" s="10">
         <f>G29/H8</f>
-        <v>165.78</v>
+        <v>181.98</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
@@ -1781,7 +1780,7 @@
       <c r="O30" s="5"/>
       <c r="Q30" s="10">
         <f>Q29/H3</f>
-        <v>6.048</v>
+        <v>6.48</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -1793,14 +1792,14 @@
       </c>
       <c r="B31" s="10">
         <f>B29/H9</f>
-        <v>6804</v>
+        <v>7452</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="G31" s="10">
         <f>G29/H9</f>
-        <v>5526</v>
+        <v>6066</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -1814,7 +1813,7 @@
       <c r="O31" s="5"/>
       <c r="Q31" s="10">
         <f>Q29/H4</f>
-        <v>90.72</v>
+        <v>97.2</v>
       </c>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
@@ -1823,17 +1822,17 @@
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33">
         <f>G26/B26</f>
-        <v>4.8730158730158726</v>
+        <v>4.8840579710144931</v>
       </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="O34">
         <f>S27/N27</f>
-        <v>5.25</v>
+        <v>5.625</v>
       </c>
       <c r="P34">
         <f>S27/N27</f>
-        <v>5.25</v>
+        <v>5.625</v>
       </c>
     </row>
   </sheetData>
@@ -1849,7 +1848,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
